--- a/配置表格/X系统参数.xlsx
+++ b/配置表格/X系统参数.xlsx
@@ -11,7 +11,7 @@
     <sheet name="ConfigAssets" sheetId="2" r:id="rId2"/>
     <sheet name="说明" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="198">
   <si>
     <t>##var</t>
   </si>
@@ -285,6 +285,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>参数</t>
     </r>
     <r>
@@ -515,6 +520,79 @@
     <t>系别御兽神通名万灵御心诀每次使用御兽系别人道神通参数（万分比）概率获得1点熟练度</t>
   </si>
   <si>
+    <t>参数_系别剑道</t>
+  </si>
+  <si>
+    <r>
+      <t>该系别的技能，大图显示的图标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+  </si>
+  <si>
+    <t>参数_系别炼体</t>
+  </si>
+  <si>
+    <t>参数_系别金行</t>
+  </si>
+  <si>
+    <t>参数_系别木行</t>
+  </si>
+  <si>
+    <t>参数_系别水行</t>
+  </si>
+  <si>
+    <t>参数_系别火行</t>
+  </si>
+  <si>
+    <t>参数_系别土行</t>
+  </si>
+  <si>
+    <t>参数_系别术法</t>
+  </si>
+  <si>
+    <t>参数_系别灵植</t>
+  </si>
+  <si>
+    <t>参数_系别灵材</t>
+  </si>
+  <si>
+    <t>参数_系别炼丹</t>
+  </si>
+  <si>
+    <t>参数_系别炼器</t>
+  </si>
+  <si>
+    <t>参数_系别符箓</t>
+  </si>
+  <si>
+    <t>参数_系别阵法</t>
+  </si>
+  <si>
+    <t>参数_系别御兽</t>
+  </si>
+  <si>
+    <t>参数_系别修炼</t>
+  </si>
+  <si>
+    <t>参数_系别破境</t>
+  </si>
+  <si>
+    <t>参数_系别神识</t>
+  </si>
+  <si>
+    <t>参数_系别五行</t>
+  </si>
+  <si>
+    <t>参数_系别神通</t>
+  </si>
+  <si>
     <t>参数_走路音效_草地</t>
   </si>
   <si>
@@ -635,6 +713,42 @@
     <t>除衣服外其他所有装备，装备，卸下，挪动，丢弃都用这个音效</t>
   </si>
   <si>
+    <t>参数_玩家普攻技能</t>
+  </si>
+  <si>
+    <t>11000001</t>
+  </si>
+  <si>
+    <t>参数_玩家攻击范围</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>参数_任务重置_每日小时</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>每日任务的重置时刻：北京时间的小时（0～23），全服统一；5 即每天 05:00</t>
+  </si>
+  <si>
+    <t>参数_任务重置_每周星期</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>每周任务在星期几重置：1～7 依次为周一～周日，按北京时间；1 即周一</t>
+  </si>
+  <si>
+    <t>参数_任务重置_每周小时</t>
+  </si>
+  <si>
+    <t>每周任务的重置时刻：北京时间的小时（0～23），与 参数_任务重置_每周星期 合用；5 即 05:00</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -656,13 +770,13 @@
     <t>资源图标</t>
   </si>
   <si>
-    <t>金币</t>
+    <t>灵石</t>
   </si>
   <si>
     <t>gold</t>
   </si>
   <si>
-    <t>灵符</t>
+    <t>仙玉</t>
   </si>
   <si>
     <t>lingfu</t>
@@ -693,7 +807,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -715,6 +829,12 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1186,163 +1306,168 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1814,7 +1939,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
@@ -1824,14 +1949,20 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">config_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">param_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">param_value</t>
+        </is>
       </c>
       <c r="E1" s="1"/>
     </row>
@@ -1999,7 +2130,7 @@
       <c r="D13">
         <v>100</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2021,13 +2152,13 @@
       <c r="B15">
         <v>11</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D15">
         <v>8000</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2035,13 +2166,13 @@
       <c r="B16">
         <v>12</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D16">
-        <v>30040037</v>
-      </c>
-      <c r="E16" s="5" t="s">
+        <v>10701000</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2049,13 +2180,13 @@
       <c r="B17">
         <v>13</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D17">
-        <v>30040038</v>
-      </c>
-      <c r="E17" s="5" t="s">
+        <v>10701001</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2063,13 +2194,13 @@
       <c r="B18">
         <v>14</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="7" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2077,13 +2208,13 @@
       <c r="B19">
         <v>15</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="7" t="s">
         <v>36</v>
       </c>
       <c r="D19">
         <v>2</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="7" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2091,13 +2222,13 @@
       <c r="B20">
         <v>16</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="7" t="s">
         <v>38</v>
       </c>
       <c r="D20" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="7" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2105,13 +2236,13 @@
       <c r="B21">
         <v>17</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="7" t="s">
         <v>41</v>
       </c>
       <c r="D21">
         <v>3000</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="7" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2119,7 +2250,7 @@
       <c r="B22">
         <v>18</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="7" t="s">
         <v>43</v>
       </c>
       <c r="D22">
@@ -2133,7 +2264,7 @@
       <c r="B23">
         <v>19</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="7" t="s">
         <v>45</v>
       </c>
       <c r="D23">
@@ -2147,7 +2278,7 @@
       <c r="B24">
         <v>20</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="7" t="s">
         <v>47</v>
       </c>
       <c r="D24">
@@ -2161,7 +2292,7 @@
       <c r="B25">
         <v>21</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D25">
@@ -2175,7 +2306,7 @@
       <c r="B26">
         <v>22</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D26">
@@ -2189,7 +2320,7 @@
       <c r="B27">
         <v>23</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="7" t="s">
         <v>53</v>
       </c>
       <c r="D27">
@@ -2203,7 +2334,7 @@
       <c r="B28">
         <v>24</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="7" t="s">
         <v>55</v>
       </c>
       <c r="D28">
@@ -2217,7 +2348,7 @@
       <c r="B29">
         <v>25</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="7" t="s">
         <v>57</v>
       </c>
       <c r="D29">
@@ -2231,7 +2362,7 @@
       <c r="B30">
         <v>26</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="7" t="s">
         <v>59</v>
       </c>
       <c r="D30">
@@ -2245,7 +2376,7 @@
       <c r="B31">
         <v>27</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="7" t="s">
         <v>61</v>
       </c>
       <c r="D31">
@@ -2259,7 +2390,7 @@
       <c r="B32">
         <v>28</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="7" t="s">
         <v>63</v>
       </c>
       <c r="D32">
@@ -2273,7 +2404,7 @@
       <c r="B33">
         <v>29</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D33">
@@ -2287,7 +2418,7 @@
       <c r="B34">
         <v>30</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D34">
@@ -2301,7 +2432,7 @@
       <c r="B35">
         <v>31</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="7" t="s">
         <v>69</v>
       </c>
       <c r="D35">
@@ -2315,7 +2446,7 @@
       <c r="B36">
         <v>32</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="7" t="s">
         <v>71</v>
       </c>
       <c r="D36">
@@ -2329,7 +2460,7 @@
       <c r="B37">
         <v>33</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="7" t="s">
         <v>73</v>
       </c>
       <c r="D37">
@@ -2343,7 +2474,7 @@
       <c r="B38">
         <v>34</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="7" t="s">
         <v>75</v>
       </c>
       <c r="D38">
@@ -2357,7 +2488,7 @@
       <c r="B39">
         <v>35</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="7" t="s">
         <v>77</v>
       </c>
       <c r="D39">
@@ -2371,7 +2502,7 @@
       <c r="B40">
         <v>36</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="7" t="s">
         <v>79</v>
       </c>
       <c r="D40">
@@ -2385,7 +2516,7 @@
       <c r="B41">
         <v>37</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="7" t="s">
         <v>81</v>
       </c>
       <c r="D41">
@@ -2399,7 +2530,7 @@
       <c r="B42">
         <v>38</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="7" t="s">
         <v>83</v>
       </c>
       <c r="D42">
@@ -2413,7 +2544,7 @@
       <c r="B43">
         <v>39</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="7" t="s">
         <v>85</v>
       </c>
       <c r="D43">
@@ -2427,7 +2558,7 @@
       <c r="B44">
         <v>40</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="7" t="s">
         <v>87</v>
       </c>
       <c r="D44">
@@ -2441,7 +2572,7 @@
       <c r="B45">
         <v>41</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D45">
@@ -2455,7 +2586,7 @@
       <c r="B46">
         <v>42</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="7" t="s">
         <v>91</v>
       </c>
       <c r="D46">
@@ -2469,7 +2600,7 @@
       <c r="B47">
         <v>43</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="7" t="s">
         <v>93</v>
       </c>
       <c r="D47">
@@ -2483,7 +2614,7 @@
       <c r="B48">
         <v>44</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="7" t="s">
         <v>95</v>
       </c>
       <c r="D48">
@@ -2493,11 +2624,11 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" customFormat="1" spans="1:5">
+    <row r="49" customFormat="1" spans="2:5">
       <c r="B49">
         <v>45</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="7" t="s">
         <v>97</v>
       </c>
       <c r="D49">
@@ -2507,11 +2638,11 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" customFormat="1" spans="1:5">
+    <row r="50" customFormat="1" spans="2:5">
       <c r="B50">
         <v>46</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="7" t="s">
         <v>99</v>
       </c>
       <c r="D50">
@@ -2521,11 +2652,11 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" customFormat="1" spans="1:5">
+    <row r="51" customFormat="1" spans="2:5">
       <c r="B51">
         <v>47</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="7" t="s">
         <v>101</v>
       </c>
       <c r="D51">
@@ -2535,11 +2666,11 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" customFormat="1" spans="1:5">
+    <row r="52" customFormat="1" spans="2:5">
       <c r="B52">
         <v>48</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="7" t="s">
         <v>103</v>
       </c>
       <c r="D52">
@@ -2549,11 +2680,11 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" customFormat="1" spans="1:5">
+    <row r="53" customFormat="1" spans="2:5">
       <c r="B53">
         <v>49</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="7" t="s">
         <v>105</v>
       </c>
       <c r="D53">
@@ -2563,11 +2694,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" customFormat="1" spans="1:5">
+    <row r="54" customFormat="1" spans="2:5">
       <c r="B54">
         <v>50</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="7" t="s">
         <v>107</v>
       </c>
       <c r="D54">
@@ -2577,229 +2708,573 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2">
+    <row r="55" customFormat="1" spans="2:5">
+      <c r="B55">
+        <v>51</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="2:5">
+      <c r="B56">
+        <v>52</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56">
+        <v>14</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="2:5">
+      <c r="B57">
+        <v>53</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57">
+        <v>8</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" spans="2:5">
+      <c r="B58">
+        <v>54</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D58">
+        <v>8</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" spans="2:5">
+      <c r="B59">
+        <v>55</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59">
+        <v>8</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" spans="2:5">
+      <c r="B60">
+        <v>56</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D60">
+        <v>8</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="2:5">
+      <c r="B61">
+        <v>57</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D61">
+        <v>8</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" spans="2:5">
+      <c r="B62">
+        <v>58</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D62">
+        <v>13</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="2:5">
+      <c r="B63">
+        <v>59</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D63">
+        <v>2</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" spans="2:5">
+      <c r="B64">
+        <v>60</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" spans="1:5">
+      <c r="B65">
+        <v>61</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D65">
+        <v>4</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" spans="1:5">
+      <c r="B66">
+        <v>62</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D66">
+        <v>5</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" spans="1:5">
+      <c r="B67">
+        <v>63</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D67">
+        <v>6</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" spans="1:5">
+      <c r="B68">
+        <v>64</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D68">
+        <v>7</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" spans="1:5">
+      <c r="B69">
+        <v>65</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D69">
+        <v>9</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" spans="1:5">
+      <c r="B70">
+        <v>66</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D70">
+        <v>10</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" spans="1:5">
+      <c r="B71">
+        <v>67</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D71">
+        <v>11</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="72" customFormat="1" spans="1:5">
+      <c r="B72">
+        <v>68</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D72">
+        <v>12</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73" customFormat="1" spans="1:5">
+      <c r="B73">
+        <v>69</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D73">
+        <v>8</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="74" customFormat="1" spans="1:5">
+      <c r="B74">
+        <v>70</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D74">
+        <v>19</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2">
         <v>100</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C75" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2">
+        <v>101</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2">
+        <v>102</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2">
+        <v>103</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2">
+        <v>104</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2">
+        <v>105</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2">
+        <v>106</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2">
+        <v>107</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2">
+        <v>108</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2">
         <v>109</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="C84" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2">
         <v>110</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="C85" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2">
         <v>111</v>
       </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2">
-        <v>101</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="C86" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2">
         <v>112</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="C87" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2">
         <v>113</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="C88" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2">
         <v>114</v>
       </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2">
-        <v>102</v>
-      </c>
-      <c r="C57" s="2" t="s">
+      <c r="C89" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="B90" s="2">
         <v>115</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="C90" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="B91" s="2">
         <v>116</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2">
-        <v>103</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="C91" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="B92" s="2">
         <v>117</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="C92" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="B93" s="2">
         <v>118</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2">
-        <v>104</v>
-      </c>
-      <c r="C59" s="2" t="s">
+      <c r="C93" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="B94" s="2">
         <v>119</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2">
-        <v>105</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2">
-        <v>106</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2">
-        <v>107</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2">
-        <v>108</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2">
-        <v>109</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2">
-        <v>110</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2">
-        <v>111</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2">
-        <v>112</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2">
-        <v>113</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2">
-        <v>114</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>148</v>
+      <c r="C94" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2811,27 +3286,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" ht="15" spans="1:5">
+    <row r="1" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">config_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is_account_shared</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -2844,34 +3337,65 @@
       <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
       <c r="E3" s="2"/>
-    </row>
-    <row r="4" ht="15" spans="1:5">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>155</v>
+        <v>188</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说明</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是否账号共享（TRUE=同账号各角色共用一份余额；FALSE=角色级，随角色存档）</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2879,29 +3403,32 @@
       <c r="B5" s="2">
         <v>1000001</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>156</v>
+      <c r="C5" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>190</v>
+      </c>
+      <c r="E5" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>1000002</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>158</v>
+      <c r="C6" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1000002</v>
+        <v>192</v>
+      </c>
+      <c r="E6" s="5">
+        <v>18</v>
+      </c>
+      <c r="G6" s="5" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2918,24 +3445,24 @@
   <sheetData>
     <row r="1" ht="15" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/配置表格/X系统参数.xlsx
+++ b/配置表格/X系统参数.xlsx
@@ -1939,7 +1939,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
@@ -3275,6 +3275,156 @@
       </c>
       <c r="E94" s="2" t="s">
         <v>181</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="2">
+        <v>120</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参数_玩家脱战时长</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96">
+        <v>121</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参数_境界压制PvE步长</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比：PvE 每差一个大境界的伤害系数增量（1000=10%/境）。占位值，待策划给正式口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97">
+        <v>122</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参数_境界压制PvE下限</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2000</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比：PvE 境界修正乘区下限（2000=最低 20%）。占位值，待策划给</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98">
+        <v>123</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参数_境界压制PvE上限</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20000</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比：PvE 境界修正乘区上限（20000=最高 200%）。占位值，待策划给</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99">
+        <v>124</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参数_境界压制PvP步长</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比：PvP（双方都是玩家）每差一个大境界的增量，策划口径比 PvE 更弱。占位值，待策划给</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100">
+        <v>125</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参数_境界压制PvP下限</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5000</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比：PvP 境界修正乘区下限。占位值，待策划给</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101">
+        <v>126</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参数_境界压制PvP上限</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15000</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比：PvP 境界修正乘区上限。占位值，待策划给</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102">
+        <v>127</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参数_玩家普攻伤害点</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/配置表格/X系统参数.xlsx
+++ b/配置表格/X系统参数.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ConfigSystemVar" sheetId="1" r:id="rId1"/>
@@ -29,18 +29,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="241">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <t>ConfigID</t>
-  </si>
-  <si>
-    <t>ParamID</t>
-  </si>
-  <si>
-    <t>ParamValue</t>
+    <t>config_id</t>
+  </si>
+  <si>
+    <t>param_id</t>
+  </si>
+  <si>
+    <t>param_value</t>
   </si>
   <si>
     <t>##type</t>
@@ -524,6 +524,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>该系别的技能，大图显示的图标</t>
     </r>
     <r>
@@ -749,13 +754,130 @@
     <t>每周任务的重置时刻：北京时间的小时（0～23），与 参数_任务重置_每周星期 合用；5 即 05:00</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Icon</t>
+    <t>参数_玩家脱战时长</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>参数_境界压制PvE步长</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>万分比：PvE 每差一个大境界的伤害系数增量（1000=10%/境）。占位值，待策划给正式口径</t>
+  </si>
+  <si>
+    <t>参数_境界压制PvE下限</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>万分比：PvE 境界修正乘区下限（2000=最低 20%）。占位值，待策划给</t>
+  </si>
+  <si>
+    <t>参数_境界压制PvE上限</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>万分比：PvE 境界修正乘区上限（20000=最高 200%）。占位值，待策划给</t>
+  </si>
+  <si>
+    <t>参数_境界压制PvP步长</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>万分比：PvP（双方都是玩家）每差一个大境界的增量，策划口径比 PvE 更弱。占位值，待策划给</t>
+  </si>
+  <si>
+    <t>参数_境界压制PvP下限</t>
+  </si>
+  <si>
+    <t>万分比：PvP 境界修正乘区下限。占位值，待策划给</t>
+  </si>
+  <si>
+    <t>参数_境界压制PvP上限</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>万分比：PvP 境界修正乘区上限。占位值，待策划给</t>
+  </si>
+  <si>
+    <t>参数_玩家普攻伤害点</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>参数_制符_评分网格宽</t>
+  </si>
+  <si>
+    <t>正整数；横向评分网格数量，单位格，当前128，不是屏幕像素。</t>
+  </si>
+  <si>
+    <t>参数_制符_评分网格高</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>正整数；纵向评分网格数量，单位格，当前192。</t>
+  </si>
+  <si>
+    <t>参数_制符_评分容差</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>非负整数；评分网格中的像素容差，当前2；不允许空值。</t>
+  </si>
+  <si>
+    <t>参数_制符_覆盖率权重</t>
+  </si>
+  <si>
+    <t>7000</t>
+  </si>
+  <si>
+    <t>整数万分比，0至10000；与贴合率权重合计10000，当前7000。</t>
+  </si>
+  <si>
+    <t>参数_制符_贴合率权重</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>整数万分比，0至10000；与覆盖率权重合计10000，当前3000。</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>is_account_shared</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
   <si>
     <t>资源ID</t>
@@ -770,6 +892,12 @@
     <t>资源图标</t>
   </si>
   <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>是否账号共享（TRUE=同账号各角色共用一份余额；FALSE=角色级，随角色存档）</t>
+  </si>
+  <si>
     <t>灵石</t>
   </si>
   <si>
@@ -780,6 +908,12 @@
   </si>
   <si>
     <t>lingfu</t>
+  </si>
+  <si>
+    <t>宗门贡献</t>
+  </si>
+  <si>
+    <t>gongxian</t>
   </si>
   <si>
     <t>版本号</t>
@@ -1452,7 +1586,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1461,13 +1595,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1752,7 +1889,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -1939,30 +2076,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
+    <col min="5" max="5" width="64" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">config_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">param_id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">param_value</t>
-        </is>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="E1" s="1"/>
     </row>
@@ -2130,7 +2262,7 @@
       <c r="D13">
         <v>100</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="7" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2152,13 +2284,13 @@
       <c r="B15">
         <v>11</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D15">
         <v>8000</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="7" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2166,13 +2298,13 @@
       <c r="B16">
         <v>12</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D16">
         <v>10701000</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2180,13 +2312,13 @@
       <c r="B17">
         <v>13</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D17">
         <v>10701001</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2194,13 +2326,13 @@
       <c r="B18">
         <v>14</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>34</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2208,13 +2340,13 @@
       <c r="B19">
         <v>15</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D19">
         <v>2</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2222,13 +2354,13 @@
       <c r="B20">
         <v>16</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>38</v>
       </c>
       <c r="D20" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="8" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2236,13 +2368,13 @@
       <c r="B21">
         <v>17</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>41</v>
       </c>
       <c r="D21">
         <v>3000</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2250,7 +2382,7 @@
       <c r="B22">
         <v>18</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>43</v>
       </c>
       <c r="D22">
@@ -2264,7 +2396,7 @@
       <c r="B23">
         <v>19</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D23">
@@ -2278,7 +2410,7 @@
       <c r="B24">
         <v>20</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D24">
@@ -2292,7 +2424,7 @@
       <c r="B25">
         <v>21</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>49</v>
       </c>
       <c r="D25">
@@ -2306,7 +2438,7 @@
       <c r="B26">
         <v>22</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="8" t="s">
         <v>51</v>
       </c>
       <c r="D26">
@@ -2320,7 +2452,7 @@
       <c r="B27">
         <v>23</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="8" t="s">
         <v>53</v>
       </c>
       <c r="D27">
@@ -2334,7 +2466,7 @@
       <c r="B28">
         <v>24</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>55</v>
       </c>
       <c r="D28">
@@ -2348,7 +2480,7 @@
       <c r="B29">
         <v>25</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>57</v>
       </c>
       <c r="D29">
@@ -2362,7 +2494,7 @@
       <c r="B30">
         <v>26</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="8" t="s">
         <v>59</v>
       </c>
       <c r="D30">
@@ -2376,7 +2508,7 @@
       <c r="B31">
         <v>27</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D31">
@@ -2390,7 +2522,7 @@
       <c r="B32">
         <v>28</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>63</v>
       </c>
       <c r="D32">
@@ -2404,7 +2536,7 @@
       <c r="B33">
         <v>29</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="8" t="s">
         <v>65</v>
       </c>
       <c r="D33">
@@ -2418,7 +2550,7 @@
       <c r="B34">
         <v>30</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="8" t="s">
         <v>67</v>
       </c>
       <c r="D34">
@@ -2432,7 +2564,7 @@
       <c r="B35">
         <v>31</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="8" t="s">
         <v>69</v>
       </c>
       <c r="D35">
@@ -2446,7 +2578,7 @@
       <c r="B36">
         <v>32</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="8" t="s">
         <v>71</v>
       </c>
       <c r="D36">
@@ -2460,7 +2592,7 @@
       <c r="B37">
         <v>33</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D37">
@@ -2474,7 +2606,7 @@
       <c r="B38">
         <v>34</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="8" t="s">
         <v>75</v>
       </c>
       <c r="D38">
@@ -2488,7 +2620,7 @@
       <c r="B39">
         <v>35</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="8" t="s">
         <v>77</v>
       </c>
       <c r="D39">
@@ -2502,7 +2634,7 @@
       <c r="B40">
         <v>36</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D40">
@@ -2516,7 +2648,7 @@
       <c r="B41">
         <v>37</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="8" t="s">
         <v>81</v>
       </c>
       <c r="D41">
@@ -2530,7 +2662,7 @@
       <c r="B42">
         <v>38</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="8" t="s">
         <v>83</v>
       </c>
       <c r="D42">
@@ -2544,7 +2676,7 @@
       <c r="B43">
         <v>39</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="8" t="s">
         <v>85</v>
       </c>
       <c r="D43">
@@ -2558,7 +2690,7 @@
       <c r="B44">
         <v>40</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="8" t="s">
         <v>87</v>
       </c>
       <c r="D44">
@@ -2572,7 +2704,7 @@
       <c r="B45">
         <v>41</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="8" t="s">
         <v>89</v>
       </c>
       <c r="D45">
@@ -2586,7 +2718,7 @@
       <c r="B46">
         <v>42</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="8" t="s">
         <v>91</v>
       </c>
       <c r="D46">
@@ -2600,7 +2732,7 @@
       <c r="B47">
         <v>43</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="8" t="s">
         <v>93</v>
       </c>
       <c r="D47">
@@ -2614,7 +2746,7 @@
       <c r="B48">
         <v>44</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="8" t="s">
         <v>95</v>
       </c>
       <c r="D48">
@@ -2628,7 +2760,7 @@
       <c r="B49">
         <v>45</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="8" t="s">
         <v>97</v>
       </c>
       <c r="D49">
@@ -2642,7 +2774,7 @@
       <c r="B50">
         <v>46</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="8" t="s">
         <v>99</v>
       </c>
       <c r="D50">
@@ -2656,7 +2788,7 @@
       <c r="B51">
         <v>47</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D51">
@@ -2670,7 +2802,7 @@
       <c r="B52">
         <v>48</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="8" t="s">
         <v>103</v>
       </c>
       <c r="D52">
@@ -2684,7 +2816,7 @@
       <c r="B53">
         <v>49</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="8" t="s">
         <v>105</v>
       </c>
       <c r="D53">
@@ -2698,7 +2830,7 @@
       <c r="B54">
         <v>50</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D54">
@@ -2712,13 +2844,13 @@
       <c r="B55">
         <v>51</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="8" t="s">
         <v>109</v>
       </c>
       <c r="D55">
         <v>1</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2726,13 +2858,13 @@
       <c r="B56">
         <v>52</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="8" t="s">
         <v>111</v>
       </c>
       <c r="D56">
         <v>14</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2740,13 +2872,13 @@
       <c r="B57">
         <v>53</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D57">
         <v>8</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2754,13 +2886,13 @@
       <c r="B58">
         <v>54</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="8" t="s">
         <v>113</v>
       </c>
       <c r="D58">
         <v>8</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2768,13 +2900,13 @@
       <c r="B59">
         <v>55</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D59">
         <v>8</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2782,13 +2914,13 @@
       <c r="B60">
         <v>56</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="8" t="s">
         <v>115</v>
       </c>
       <c r="D60">
         <v>8</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E60" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2796,13 +2928,13 @@
       <c r="B61">
         <v>57</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="8" t="s">
         <v>116</v>
       </c>
       <c r="D61">
         <v>8</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2810,13 +2942,13 @@
       <c r="B62">
         <v>58</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="8" t="s">
         <v>117</v>
       </c>
       <c r="D62">
         <v>13</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2824,13 +2956,13 @@
       <c r="B63">
         <v>59</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="8" t="s">
         <v>118</v>
       </c>
       <c r="D63">
         <v>2</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2838,13 +2970,13 @@
       <c r="B64">
         <v>60</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="8" t="s">
         <v>119</v>
       </c>
       <c r="D64">
         <v>3</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2852,13 +2984,13 @@
       <c r="B65">
         <v>61</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="8" t="s">
         <v>120</v>
       </c>
       <c r="D65">
         <v>4</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E65" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2866,13 +2998,13 @@
       <c r="B66">
         <v>62</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="8" t="s">
         <v>121</v>
       </c>
       <c r="D66">
         <v>5</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2880,13 +3012,13 @@
       <c r="B67">
         <v>63</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="8" t="s">
         <v>122</v>
       </c>
       <c r="D67">
         <v>6</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2894,13 +3026,13 @@
       <c r="B68">
         <v>64</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="8" t="s">
         <v>123</v>
       </c>
       <c r="D68">
         <v>7</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2908,13 +3040,13 @@
       <c r="B69">
         <v>65</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="8" t="s">
         <v>124</v>
       </c>
       <c r="D69">
         <v>9</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2922,13 +3054,13 @@
       <c r="B70">
         <v>66</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="8" t="s">
         <v>125</v>
       </c>
       <c r="D70">
         <v>10</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2936,13 +3068,13 @@
       <c r="B71">
         <v>67</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="8" t="s">
         <v>126</v>
       </c>
       <c r="D71">
         <v>11</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2950,13 +3082,13 @@
       <c r="B72">
         <v>68</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="8" t="s">
         <v>127</v>
       </c>
       <c r="D72">
         <v>12</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2964,13 +3096,13 @@
       <c r="B73">
         <v>69</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C73" s="8" t="s">
         <v>128</v>
       </c>
       <c r="D73">
         <v>8</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2978,13 +3110,13 @@
       <c r="B74">
         <v>70</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="8" t="s">
         <v>129</v>
       </c>
       <c r="D74">
         <v>19</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -3277,154 +3409,180 @@
         <v>181</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:5">
       <c r="B95" s="2">
         <v>120</v>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参数_玩家脱战时长</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5000</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
+      <c r="C95" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="B96">
         <v>121</v>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参数_境界压制PvE步长</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">万分比：PvE 每差一个大境界的伤害系数增量（1000=10%/境）。占位值，待策划给正式口径</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
+      <c r="C96" t="s">
+        <v>184</v>
+      </c>
+      <c r="D96" t="s">
+        <v>185</v>
+      </c>
+      <c r="E96" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5">
       <c r="B97">
         <v>122</v>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参数_境界压制PvE下限</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2000</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">万分比：PvE 境界修正乘区下限（2000=最低 20%）。占位值，待策划给</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
+      <c r="C97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D97" t="s">
+        <v>188</v>
+      </c>
+      <c r="E97" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5">
       <c r="B98">
         <v>123</v>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参数_境界压制PvE上限</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20000</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">万分比：PvE 境界修正乘区上限（20000=最高 200%）。占位值，待策划给</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
+      <c r="C98" t="s">
+        <v>190</v>
+      </c>
+      <c r="D98" t="s">
+        <v>191</v>
+      </c>
+      <c r="E98" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5">
       <c r="B99">
         <v>124</v>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参数_境界压制PvP步长</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">500</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">万分比：PvP（双方都是玩家）每差一个大境界的增量，策划口径比 PvE 更弱。占位值，待策划给</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
+      <c r="C99" t="s">
+        <v>193</v>
+      </c>
+      <c r="D99" t="s">
+        <v>194</v>
+      </c>
+      <c r="E99" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5">
       <c r="B100">
         <v>125</v>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参数_境界压制PvP下限</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5000</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">万分比：PvP 境界修正乘区下限。占位值，待策划给</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
+      <c r="C100" t="s">
+        <v>196</v>
+      </c>
+      <c r="D100" t="s">
+        <v>183</v>
+      </c>
+      <c r="E100" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5">
       <c r="B101">
         <v>126</v>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参数_境界压制PvP上限</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15000</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">万分比：PvP 境界修正乘区上限。占位值，待策划给</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
+      <c r="C101" t="s">
+        <v>198</v>
+      </c>
+      <c r="D101" t="s">
+        <v>199</v>
+      </c>
+      <c r="E101" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5">
       <c r="B102">
         <v>127</v>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参数_玩家普攻伤害点</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400</t>
-        </is>
+      <c r="C102" t="s">
+        <v>201</v>
+      </c>
+      <c r="D102" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="103" ht="66" customHeight="1" spans="2:5">
+      <c r="B103">
+        <v>130</v>
+      </c>
+      <c r="C103" t="s">
+        <v>203</v>
+      </c>
+      <c r="D103" t="s">
+        <v>173</v>
+      </c>
+      <c r="E103" s="9" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="104" ht="66" customHeight="1" spans="2:5">
+      <c r="B104">
+        <v>131</v>
+      </c>
+      <c r="C104" t="s">
+        <v>205</v>
+      </c>
+      <c r="D104" t="s">
+        <v>206</v>
+      </c>
+      <c r="E104" s="9" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="105" ht="66" customHeight="1" spans="2:5">
+      <c r="B105">
+        <v>132</v>
+      </c>
+      <c r="C105" t="s">
+        <v>208</v>
+      </c>
+      <c r="D105" t="s">
+        <v>209</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="106" ht="66" customHeight="1" spans="2:5">
+      <c r="B106">
+        <v>133</v>
+      </c>
+      <c r="C106" t="s">
+        <v>211</v>
+      </c>
+      <c r="D106" t="s">
+        <v>212</v>
+      </c>
+      <c r="E106" s="9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="107" ht="66" customHeight="1" spans="2:5">
+      <c r="B107">
+        <v>134</v>
+      </c>
+      <c r="C107" t="s">
+        <v>214</v>
+      </c>
+      <c r="D107" t="s">
+        <v>215</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -3436,45 +3594,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="6"/>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" ht="15" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">config_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">desc</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">is_account_shared</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -3487,92 +3633,78 @@
       <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bool</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
+      <c r="D3" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15">
+      <c r="G3" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:7">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">说明</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否账号共享（TRUE=同账号各角色共用一份余额；FALSE=角色级，随角色存档）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>227</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1000001</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>190</v>
+        <v>231</v>
       </c>
       <c r="E5" s="5">
         <v>17</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>1000002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="E6" s="5">
         <v>18</v>
@@ -3580,6 +3712,18 @@
       <c r="G6" s="5" t="b">
         <v>1</v>
       </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7" s="2">
+        <v>1000003</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D7" t="s">
+        <v>235</v>
+      </c>
+      <c r="G7" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3595,24 +3739,24 @@
   <sheetData>
     <row r="1" ht="15" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>196</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
-        <v>197</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/配置表格/X系统参数.xlsx
+++ b/配置表格/X系统参数.xlsx
@@ -10,6 +10,8 @@
     <sheet name="ConfigSystemVar" sheetId="1" r:id="rId1"/>
     <sheet name="ConfigAssets" sheetId="2" r:id="rId2"/>
     <sheet name="说明" sheetId="3" r:id="rId3"/>
+    <sheet name="境界压制复算" sheetId="4" r:id="rIdConfig4"/>
+    <sheet name="共用表处理总览" sheetId="5" r:id="rIdConfig5"/>
   </sheets>
   <calcPr calcId="191029" calcCompleted="0" calcOnSave="0"/>
   <extLst>
@@ -941,7 +943,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1122,8 +1124,36 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1328,8 +1358,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1435,8 +1487,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1585,8 +1651,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="9"/>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="10"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1603,6 +1671,35 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="9" xfId="50"/>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="9" xfId="50">
+      <extLst>
+        <ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="9" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="9" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="9" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="9" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="10" xfId="51"/>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="10" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="10" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="10" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="10" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2076,7 +2173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
@@ -2201,8 +2298,8 @@
       <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="2">
-        <v>10310001</v>
+      <c r="D9" t="n" s="2">
+        <v>10130100</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
@@ -3430,8 +3527,8 @@
       <c r="D96" t="s">
         <v>185</v>
       </c>
-      <c r="E96" t="s">
-        <v>186</v>
+      <c r="E96" t="str">
+        <v>本轮首版暂定；保留原值以控制变化范围。PvE步长1000/下限2000/上限20000；PvP步长500/下限5000/上限15000。详见境界压制复算。</v>
       </c>
     </row>
     <row r="97" spans="2:5">
@@ -3444,8 +3541,8 @@
       <c r="D97" t="s">
         <v>188</v>
       </c>
-      <c r="E97" t="s">
-        <v>189</v>
+      <c r="E97" t="str">
+        <v>本轮首版暂定；保留原值以控制变化范围。PvE步长1000/下限2000/上限20000；PvP步长500/下限5000/上限15000。详见境界压制复算。</v>
       </c>
     </row>
     <row r="98" spans="2:5">
@@ -3458,8 +3555,8 @@
       <c r="D98" t="s">
         <v>191</v>
       </c>
-      <c r="E98" t="s">
-        <v>192</v>
+      <c r="E98" t="str">
+        <v>本轮首版暂定；保留原值以控制变化范围。PvE步长1000/下限2000/上限20000；PvP步长500/下限5000/上限15000。详见境界压制复算。</v>
       </c>
     </row>
     <row r="99" spans="2:5">
@@ -3472,8 +3569,8 @@
       <c r="D99" t="s">
         <v>194</v>
       </c>
-      <c r="E99" t="s">
-        <v>195</v>
+      <c r="E99" t="str">
+        <v>本轮首版暂定；保留原值以控制变化范围。PvE步长1000/下限2000/上限20000；PvP步长500/下限5000/上限15000。详见境界压制复算。</v>
       </c>
     </row>
     <row r="100" spans="2:5">
@@ -3486,8 +3583,8 @@
       <c r="D100" t="s">
         <v>183</v>
       </c>
-      <c r="E100" t="s">
-        <v>197</v>
+      <c r="E100" t="str">
+        <v>本轮首版暂定；保留原值以控制变化范围。PvE步长1000/下限2000/上限20000；PvP步长500/下限5000/上限15000。详见境界压制复算。</v>
       </c>
     </row>
     <row r="101" spans="2:5">
@@ -3500,8 +3597,8 @@
       <c r="D101" t="s">
         <v>199</v>
       </c>
-      <c r="E101" t="s">
-        <v>200</v>
+      <c r="E101" t="str">
+        <v>本轮首版暂定；保留原值以控制变化范围。PvE步长1000/下限2000/上限20000；PvP步长500/下限5000/上限15000。详见境界压制复算。</v>
       </c>
     </row>
     <row r="102" spans="2:5">
@@ -3583,6 +3680,26 @@
       </c>
       <c r="E107" s="9" t="s">
         <v>216</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108">
+        <v>135</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参数_符箓替身状态识别ID</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209200</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">替身保护识别组：取消下一次整次暴击伤害；多个组使用逗号分隔。</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3691,8 +3808,14 @@
       <c r="D5" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" t="n" s="5">
         <v>17</v>
+      </c>
+      <c r="F5" t="str">
+        <v>角色级灵石钱包；掉落方案灵石直接入角色钱包，物品灵石袋的使用另按功能处理。</v>
+      </c>
+      <c r="G5" t="b" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3706,10 +3829,13 @@
       <c r="D6" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" t="n" s="5">
         <v>18</v>
       </c>
-      <c r="G6" s="5" t="b">
+      <c r="F6" t="str">
+        <v>账号共享仙玉；保持既有币种ID1000002与key，不迁移或复用。</v>
+      </c>
+      <c r="G6" t="b" s="5">
         <v>1</v>
       </c>
     </row>
@@ -3723,7 +3849,15 @@
       <c r="D7" t="s">
         <v>235</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="E7" t="n" s="5">
+        <v>17</v>
+      </c>
+      <c r="F7" t="str">
+        <v>角色级宗门贡献；上交与兑换使用同一余额。图标暂复用灵石图标17，专用图标列资源需求。</v>
+      </c>
+      <c r="G7" t="b" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3763,4 +3897,1518 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="40" customHeight="1">
+      <x:c r="A1" s="20" t="str">
+        <x:v>攻方境界</x:v>
+      </x:c>
+      <x:c r="B1" s="20" t="str">
+        <x:v>守方境界</x:v>
+      </x:c>
+      <x:c r="C1" s="20" t="str">
+        <x:v>差值</x:v>
+      </x:c>
+      <x:c r="D1" s="20" t="str">
+        <x:v>PvE万分比</x:v>
+      </x:c>
+      <x:c r="E1" s="20" t="str">
+        <x:v>PvP万分比</x:v>
+      </x:c>
+      <x:c r="F1" s="20" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="53" customHeight="1">
+      <x:c r="A2" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D2" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="E2" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F2" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="53" customHeight="1">
+      <x:c r="A3" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B3" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="18" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D3" s="18" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="E3" s="18" t="n">
+        <x:v>9500</x:v>
+      </x:c>
+      <x:c r="F3" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="53" customHeight="1">
+      <x:c r="A4" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C4" s="18" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="D4" s="18" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="E4" s="18" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="F4" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="53" customHeight="1">
+      <x:c r="A5" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="18" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="D5" s="18" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="E5" s="18" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="F5" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="53" customHeight="1">
+      <x:c r="A6" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B6" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="18" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="D6" s="18" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="E6" s="18" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="F6" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="53" customHeight="1">
+      <x:c r="A7" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B7" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C7" s="18" t="n">
+        <x:v>-5</x:v>
+      </x:c>
+      <x:c r="D7" s="18" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="E7" s="18" t="n">
+        <x:v>7500</x:v>
+      </x:c>
+      <x:c r="F7" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="53" customHeight="1">
+      <x:c r="A8" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B8" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C8" s="18" t="n">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="D8" s="18" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="E8" s="18" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="F8" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="53" customHeight="1">
+      <x:c r="A9" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B9" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="n">
+        <x:v>-7</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="E9" s="18" t="n">
+        <x:v>6500</x:v>
+      </x:c>
+      <x:c r="F9" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="53" customHeight="1">
+      <x:c r="A10" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B10" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="n">
+        <x:v>10500</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="53" customHeight="1">
+      <x:c r="A11" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B11" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="53" customHeight="1">
+      <x:c r="A12" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B12" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="n">
+        <x:v>9500</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="53" customHeight="1">
+      <x:c r="A13" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B13" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="F13" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="53" customHeight="1">
+      <x:c r="A14" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B14" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="F14" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="53" customHeight="1">
+      <x:c r="A15" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B15" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="E15" s="18" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="F15" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="53" customHeight="1">
+      <x:c r="A16" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B16" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C16" s="18" t="n">
+        <x:v>-5</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="E16" s="18" t="n">
+        <x:v>7500</x:v>
+      </x:c>
+      <x:c r="F16" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="53" customHeight="1">
+      <x:c r="A17" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B17" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C17" s="18" t="n">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="E17" s="18" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="F17" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="53" customHeight="1">
+      <x:c r="A18" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B18" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="E18" s="18" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="F18" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="53" customHeight="1">
+      <x:c r="A19" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B19" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C19" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="E19" s="18" t="n">
+        <x:v>10500</x:v>
+      </x:c>
+      <x:c r="F19" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="53" customHeight="1">
+      <x:c r="A20" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B20" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C20" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="E20" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F20" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="53" customHeight="1">
+      <x:c r="A21" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B21" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="18" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="E21" s="18" t="n">
+        <x:v>9500</x:v>
+      </x:c>
+      <x:c r="F21" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="53" customHeight="1">
+      <x:c r="A22" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B22" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C22" s="18" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="E22" s="18" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="F22" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="53" customHeight="1">
+      <x:c r="A23" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B23" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C23" s="18" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="E23" s="18" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="F23" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="53" customHeight="1">
+      <x:c r="A24" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B24" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C24" s="18" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="E24" s="18" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="F24" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="53" customHeight="1">
+      <x:c r="A25" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B25" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C25" s="18" t="n">
+        <x:v>-5</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="E25" s="18" t="n">
+        <x:v>7500</x:v>
+      </x:c>
+      <x:c r="F25" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="53" customHeight="1">
+      <x:c r="A26" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B26" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C26" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="n">
+        <x:v>13000</x:v>
+      </x:c>
+      <x:c r="E26" s="18" t="n">
+        <x:v>11500</x:v>
+      </x:c>
+      <x:c r="F26" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="53" customHeight="1">
+      <x:c r="A27" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B27" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C27" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="E27" s="18" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="F27" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="53" customHeight="1">
+      <x:c r="A28" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B28" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C28" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="E28" s="18" t="n">
+        <x:v>10500</x:v>
+      </x:c>
+      <x:c r="F28" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="53" customHeight="1">
+      <x:c r="A29" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B29" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="E29" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F29" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="53" customHeight="1">
+      <x:c r="A30" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B30" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C30" s="18" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="E30" s="18" t="n">
+        <x:v>9500</x:v>
+      </x:c>
+      <x:c r="F30" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="53" customHeight="1">
+      <x:c r="A31" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B31" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C31" s="18" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="D31" s="18" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="E31" s="18" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="F31" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="53" customHeight="1">
+      <x:c r="A32" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B32" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C32" s="18" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="D32" s="18" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="E32" s="18" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="F32" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="53" customHeight="1">
+      <x:c r="A33" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B33" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C33" s="18" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="D33" s="18" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="E33" s="18" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="F33" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="53" customHeight="1">
+      <x:c r="A34" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B34" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C34" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D34" s="18" t="n">
+        <x:v>14000</x:v>
+      </x:c>
+      <x:c r="E34" s="18" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="F34" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="53" customHeight="1">
+      <x:c r="A35" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B35" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C35" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D35" s="18" t="n">
+        <x:v>13000</x:v>
+      </x:c>
+      <x:c r="E35" s="18" t="n">
+        <x:v>11500</x:v>
+      </x:c>
+      <x:c r="F35" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="53" customHeight="1">
+      <x:c r="A36" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B36" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C36" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D36" s="18" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="E36" s="18" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="F36" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="53" customHeight="1">
+      <x:c r="A37" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B37" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D37" s="18" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="E37" s="18" t="n">
+        <x:v>10500</x:v>
+      </x:c>
+      <x:c r="F37" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="53" customHeight="1">
+      <x:c r="A38" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B38" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C38" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="E38" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F38" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="53" customHeight="1">
+      <x:c r="A39" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B39" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C39" s="18" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D39" s="18" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="E39" s="18" t="n">
+        <x:v>9500</x:v>
+      </x:c>
+      <x:c r="F39" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="53" customHeight="1">
+      <x:c r="A40" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B40" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C40" s="18" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="D40" s="18" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="E40" s="18" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="F40" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="53" customHeight="1">
+      <x:c r="A41" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B41" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C41" s="18" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="D41" s="18" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="E41" s="18" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="F41" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="53" customHeight="1">
+      <x:c r="A42" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B42" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C42" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D42" s="18" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+      <x:c r="E42" s="18" t="n">
+        <x:v>12500</x:v>
+      </x:c>
+      <x:c r="F42" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="53" customHeight="1">
+      <x:c r="A43" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B43" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C43" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D43" s="18" t="n">
+        <x:v>14000</x:v>
+      </x:c>
+      <x:c r="E43" s="18" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="F43" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="53" customHeight="1">
+      <x:c r="A44" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B44" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C44" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D44" s="18" t="n">
+        <x:v>13000</x:v>
+      </x:c>
+      <x:c r="E44" s="18" t="n">
+        <x:v>11500</x:v>
+      </x:c>
+      <x:c r="F44" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="53" customHeight="1">
+      <x:c r="A45" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B45" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D45" s="18" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="E45" s="18" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="F45" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="53" customHeight="1">
+      <x:c r="A46" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B46" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C46" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D46" s="18" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="E46" s="18" t="n">
+        <x:v>10500</x:v>
+      </x:c>
+      <x:c r="F46" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="53" customHeight="1">
+      <x:c r="A47" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B47" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C47" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D47" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="E47" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F47" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="53" customHeight="1">
+      <x:c r="A48" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B48" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C48" s="18" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D48" s="18" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="E48" s="18" t="n">
+        <x:v>9500</x:v>
+      </x:c>
+      <x:c r="F48" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="53" customHeight="1">
+      <x:c r="A49" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B49" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C49" s="18" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="D49" s="18" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="E49" s="18" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="F49" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="53" customHeight="1">
+      <x:c r="A50" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B50" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C50" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D50" s="18" t="n">
+        <x:v>16000</x:v>
+      </x:c>
+      <x:c r="E50" s="18" t="n">
+        <x:v>13000</x:v>
+      </x:c>
+      <x:c r="F50" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="53" customHeight="1">
+      <x:c r="A51" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B51" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C51" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D51" s="18" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+      <x:c r="E51" s="18" t="n">
+        <x:v>12500</x:v>
+      </x:c>
+      <x:c r="F51" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="53" customHeight="1">
+      <x:c r="A52" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B52" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C52" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D52" s="18" t="n">
+        <x:v>14000</x:v>
+      </x:c>
+      <x:c r="E52" s="18" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="F52" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="53" customHeight="1">
+      <x:c r="A53" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B53" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C53" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D53" s="18" t="n">
+        <x:v>13000</x:v>
+      </x:c>
+      <x:c r="E53" s="18" t="n">
+        <x:v>11500</x:v>
+      </x:c>
+      <x:c r="F53" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="53" customHeight="1">
+      <x:c r="A54" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B54" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C54" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D54" s="18" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="E54" s="18" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="F54" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="53" customHeight="1">
+      <x:c r="A55" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B55" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C55" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D55" s="18" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="E55" s="18" t="n">
+        <x:v>10500</x:v>
+      </x:c>
+      <x:c r="F55" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="53" customHeight="1">
+      <x:c r="A56" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B56" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C56" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D56" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="E56" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F56" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="53" customHeight="1">
+      <x:c r="A57" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B57" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C57" s="18" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D57" s="18" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="E57" s="18" t="n">
+        <x:v>9500</x:v>
+      </x:c>
+      <x:c r="F57" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="53" customHeight="1">
+      <x:c r="A58" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B58" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C58" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D58" s="18" t="n">
+        <x:v>17000</x:v>
+      </x:c>
+      <x:c r="E58" s="18" t="n">
+        <x:v>13500</x:v>
+      </x:c>
+      <x:c r="F58" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="53" customHeight="1">
+      <x:c r="A59" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B59" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C59" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D59" s="18" t="n">
+        <x:v>16000</x:v>
+      </x:c>
+      <x:c r="E59" s="18" t="n">
+        <x:v>13000</x:v>
+      </x:c>
+      <x:c r="F59" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="53" customHeight="1">
+      <x:c r="A60" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B60" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C60" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D60" s="18" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+      <x:c r="E60" s="18" t="n">
+        <x:v>12500</x:v>
+      </x:c>
+      <x:c r="F60" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="53" customHeight="1">
+      <x:c r="A61" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B61" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C61" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D61" s="18" t="n">
+        <x:v>14000</x:v>
+      </x:c>
+      <x:c r="E61" s="18" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="F61" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="53" customHeight="1">
+      <x:c r="A62" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B62" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C62" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D62" s="18" t="n">
+        <x:v>13000</x:v>
+      </x:c>
+      <x:c r="E62" s="18" t="n">
+        <x:v>11500</x:v>
+      </x:c>
+      <x:c r="F62" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="53" customHeight="1">
+      <x:c r="A63" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B63" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C63" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D63" s="18" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="E63" s="18" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="F63" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="53" customHeight="1">
+      <x:c r="A64" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B64" s="18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C64" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D64" s="18" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="E64" s="18" t="n">
+        <x:v>10500</x:v>
+      </x:c>
+      <x:c r="F64" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="53" customHeight="1">
+      <x:c r="A65" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B65" s="18" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C65" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D65" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="E65" s="18" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F65" s="18" t="str">
+        <x:v>确定性公式复算，不含伤害公式、装备和技能</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="40" customHeight="1">
+      <x:c r="A1" s="20" t="str">
+        <x:v>工作簿</x:v>
+      </x:c>
+      <x:c r="B1" s="20" t="str">
+        <x:v>处理</x:v>
+      </x:c>
+      <x:c r="C1" s="20" t="str">
+        <x:v>有效范围与依据</x:v>
+      </x:c>
+      <x:c r="D1" s="20" t="str">
+        <x:v>接入或资源需求</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="38" customHeight="1">
+      <x:c r="A2" s="18" t="str">
+        <x:v>W物品表</x:v>
+      </x:c>
+      <x:c r="B2" s="18" t="str">
+        <x:v>493本技能书目标逐项映射、140激活道具、4幻化映射</x:v>
+      </x:c>
+      <x:c r="C2" s="18" t="str">
+        <x:v>保持10153原ID不动，新增ID按实际编号公式</x:v>
+      </x:c>
+      <x:c r="D2" s="18" t="str">
+        <x:v>技能书消费接口必须对应行ID契约；真假意通过item_id反查</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="38" customHeight="1">
+      <x:c r="A3" s="18" t="str">
+        <x:v>X系统参数</x:v>
+      </x:c>
+      <x:c r="B3" s="18" t="str">
+        <x:v>6项压制首版提案、3货币说明和归属</x:v>
+      </x:c>
+      <x:c r="C3" s="18" t="str">
+        <x:v>64境界配对离线复算；不声称平衡达标</x:v>
+      </x:c>
+      <x:c r="D3" s="18" t="str">
+        <x:v>贡献专用图标；伤害上下限与单值公式冲突须在程序接入统一</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="38" customHeight="1">
+      <x:c r="A4" s="18" t="str">
+        <x:v>S属性配置表</x:v>
+      </x:c>
+      <x:c r="B4" s="18" t="str">
+        <x:v>87项完整口径对照与空说明补齐</x:v>
+      </x:c>
+      <x:c r="C4" s="18" t="str">
+        <x:v>不重排、不删现行17条炼丹与五行新增属性</x:v>
+      </x:c>
+      <x:c r="D4" s="18" t="str">
+        <x:v>前后摇/攻速整数单位等接口明细仍需程序核验</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="53" customHeight="1">
+      <x:c r="A5" s="18" t="str">
+        <x:v>J境界角色属性表</x:v>
+      </x:c>
+      <x:c r="B5" s="18" t="str">
+        <x:v>80节点突破候选和收益复算</x:v>
+      </x:c>
+      <x:c r="C5" s="18" t="str">
+        <x:v>正式三味必需；小10候选、大15候选；Lv80封顶</x:v>
+      </x:c>
+      <x:c r="D5" s="18" t="str">
+        <x:v>顶级按钮封顶与单槽丹药/三味库存必须程序验收</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="38" customHeight="1">
+      <x:c r="A6" s="18" t="str">
+        <x:v>J角色属性表</x:v>
+      </x:c>
+      <x:c r="B6" s="18" t="str">
+        <x:v>与80级境界入口对齐、停用81—85旧行</x:v>
+      </x:c>
+      <x:c r="C6" s="18" t="str">
+        <x:v>每行仍为升级增量，不改成累计属性</x:v>
+      </x:c>
+      <x:c r="D6" s="18" t="str">
+        <x:v>保留兼容入口，消费者应统一以realm_config为准</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="38" customHeight="1">
+      <x:c r="A7" s="18" t="str">
+        <x:v>R热键配置表</x:v>
+      </x:c>
+      <x:c r="B7" s="18" t="str">
+        <x:v>保留18条已完整默认热键</x:v>
+      </x:c>
+      <x:c r="C7" s="18" t="str">
+        <x:v>主副键、修饰掩码、可改键及无默认键明确</x:v>
+      </x:c>
+      <x:c r="D7" s="18" t="str">
+        <x:v>不新增未登记ActionId；按键冲突检查</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="38" customHeight="1">
+      <x:c r="A8" s="18" t="str">
+        <x:v>T图标配置表</x:v>
+      </x:c>
+      <x:c r="B8" s="18" t="str">
+        <x:v>保留合法819条图标登记</x:v>
+      </x:c>
+      <x:c r="C8" s="18" t="str">
+        <x:v>全10153物品现有icon_id引用均命中</x:v>
+      </x:c>
+      <x:c r="D8" s="18" t="str">
+        <x:v>表内命中不证明图像文件存在；新真意复用现有图标</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="38" customHeight="1">
+      <x:c r="A9" s="18" t="str">
+        <x:v>Z模型配置表</x:v>
+      </x:c>
+      <x:c r="B9" s="18" t="str">
+        <x:v>保留现有模型登记</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="str">
+        <x:v>不假造已交付模型路径</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="str">
+        <x:v>新增怪物/幻化/实体按各组需求制作资源</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="38" customHeight="1">
+      <x:c r="A10" s="18" t="str">
+        <x:v>Y音频配置表</x:v>
+      </x:c>
+      <x:c r="B10" s="18" t="str">
+        <x:v>保留现有音效9条</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="str">
+        <x:v>分类+序号主键、路径、音量、时长校验</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="str">
+        <x:v>不凭名字虚构新增文件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="38" customHeight="1">
+      <x:c r="A11" s="18" t="str">
+        <x:v>__beans__</x:v>
+      </x:c>
+      <x:c r="B11" s="18" t="str">
+        <x:v>保留源Schema，核对新增值均有bean能力</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="str">
+        <x:v>无程序接入的新设计sheet不伪装现有bean</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="str">
+        <x:v>扩展机制需求按分组说明落实</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="38" customHeight="1">
+      <x:c r="A12" s="18" t="str">
+        <x:v>__enums__</x:v>
+      </x:c>
+      <x:c r="B12" s="18" t="str">
+        <x:v>保留现有枚举取值</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="str">
+        <x:v>不迁移、不复用枚举数值</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="str">
+        <x:v>已有枚举与新字段按实际生成器复核</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="38" customHeight="1">
+      <x:c r="A13" s="18" t="str">
+        <x:v>__tables__</x:v>
+      </x:c>
+      <x:c r="B13" s="18" t="str">
+        <x:v>保留现有表登记，补充设计页不导出</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="str">
+        <x:v>表主键从登记读取，复合键不能按B列误判</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="str">
+        <x:v>灵根展示表接入需另注册明确schema</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>